--- a/extenbooks/XS001_extenbook.xlsx
+++ b/extenbooks/XS001_extenbook.xlsx
@@ -749,7 +749,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="57" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -816,7 +816,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -885,7 +885,7 @@
         <v>5.8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0999999999999998</v>
+        <v>0.09999999999999987</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -902,7 +902,7 @@
         <v>89.59999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>96.5</v>
+        <v>96.49999999999999</v>
       </c>
       <c r="D8" t="n">
         <v>6.8</v>
@@ -925,13 +925,13 @@
         <v>88.10000000000005</v>
       </c>
       <c r="C9" t="n">
-        <v>96.40000000000003</v>
+        <v>96.40000000000005</v>
       </c>
       <c r="D9" t="n">
         <v>8.199999999999998</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         <v>88.10000000000002</v>
       </c>
       <c r="C10" t="n">
-        <v>97.50000000000004</v>
+        <v>97.50000000000003</v>
       </c>
       <c r="D10" t="n">
-        <v>9.4</v>
+        <v>9.399999999999999</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -971,7 +971,7 @@
         <v>87.59999999999998</v>
       </c>
       <c r="C11" t="n">
-        <v>98.49999999999996</v>
+        <v>98.49999999999997</v>
       </c>
       <c r="D11" t="n">
         <v>10.8</v>
@@ -1023,7 +1023,7 @@
         <v>12.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0999999999999998</v>
+        <v>0.09999999999999987</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1092,7 +1092,7 @@
         <v>16.5</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0999999999999996</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1138,7 +1138,7 @@
         <v>19.4</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1000000000000007</v>
+        <v>0.1000000000000008</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1184,7 +1184,7 @@
         <v>22.3</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0999999999999996</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>177.4999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>205.8</v>
+        <v>205.7999999999999</v>
       </c>
       <c r="D24" t="n">
         <v>27</v>
@@ -1359,7 +1359,7 @@
         <v>1971</v>
       </c>
       <c r="B28" t="n">
-        <v>208.5</v>
+        <v>208.4999999999999</v>
       </c>
       <c r="C28" t="n">
         <v>243.3</v>
@@ -1434,7 +1434,7 @@
         <v>314.1000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>42.6</v>
+        <v>42.59999999999999</v>
       </c>
       <c r="E31" t="n">
         <v>1.199999999999999</v>
@@ -1566,7 +1566,7 @@
         <v>1980</v>
       </c>
       <c r="B37" t="n">
-        <v>477.1999999999997</v>
+        <v>477.1999999999996</v>
       </c>
       <c r="C37" t="n">
         <v>560.4999999999997</v>
@@ -1595,7 +1595,7 @@
         <v>653.0000000000005</v>
       </c>
       <c r="D38" t="n">
-        <v>99.20000000000005</v>
+        <v>99.20000000000003</v>
       </c>
       <c r="E38" t="n">
         <v>4.400000000000002</v>
@@ -1661,7 +1661,7 @@
         <v>767.9000000000002</v>
       </c>
       <c r="C41" t="n">
-        <v>910.7000000000004</v>
+        <v>910.7000000000003</v>
       </c>
       <c r="D41" t="n">
         <v>136</v>
@@ -1845,7 +1845,7 @@
         <v>1125.3</v>
       </c>
       <c r="C49" t="n">
-        <v>1400.200000000001</v>
+        <v>1400.2</v>
       </c>
       <c r="D49" t="n">
         <v>253.1</v>
@@ -1911,10 +1911,10 @@
         <v>1995</v>
       </c>
       <c r="B52" t="n">
-        <v>1421.799999999999</v>
+        <v>1421.8</v>
       </c>
       <c r="C52" t="n">
-        <v>1770.299999999999</v>
+        <v>1770.3</v>
       </c>
       <c r="D52" t="n">
         <v>319.4</v>
@@ -1960,7 +1960,7 @@
         <v>1739.499999999999</v>
       </c>
       <c r="C54" t="n">
-        <v>2134.8</v>
+        <v>2134.799999999999</v>
       </c>
       <c r="D54" t="n">
         <v>362.9</v>
@@ -2003,7 +2003,7 @@
         <v>1999</v>
       </c>
       <c r="B56" t="n">
-        <v>1886.9</v>
+        <v>1886.900000000001</v>
       </c>
       <c r="C56" t="n">
         <v>2342.6</v>
@@ -2233,7 +2233,7 @@
         <v>2009</v>
       </c>
       <c r="B66" t="n">
-        <v>2533.800000000001</v>
+        <v>2533.800000000002</v>
       </c>
       <c r="C66" t="n">
         <v>3218.400000000001</v>
@@ -2259,7 +2259,7 @@
         <v>2957.5</v>
       </c>
       <c r="C67" t="n">
-        <v>3627.000000000001</v>
+        <v>3627</v>
       </c>
       <c r="D67" t="n">
         <v>674.0999999999999</v>
@@ -2359,14 +2359,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="B75" t="n">
-        <v>67.29999999999998</v>
+        <v>75.10000000000002</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2382,14 +2382,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="B76" t="n">
-        <v>4</v>
+        <v>68.59999999999998</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2405,14 +2405,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="B77" t="n">
-        <v>0.1</v>
+        <v>78.90000000000002</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2428,14 +2428,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2451,14 +2451,14 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1947</v>
+        <v>1952</v>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>88.10000000000005</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2474,10 +2474,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1948</v>
+        <v>1953</v>
       </c>
       <c r="B80" t="n">
-        <v>75.10000000000002</v>
+        <v>88.10000000000002</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -2497,14 +2497,14 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1948</v>
+        <v>1954</v>
       </c>
       <c r="B81" t="n">
-        <v>79.80000000000001</v>
+        <v>87.59999999999998</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2520,14 +2520,14 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1948</v>
+        <v>1955</v>
       </c>
       <c r="B82" t="n">
-        <v>4.600000000000001</v>
+        <v>100.2</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2543,14 +2543,14 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1948</v>
+        <v>1956</v>
       </c>
       <c r="B83" t="n">
-        <v>0.1000000000000002</v>
+        <v>101.1</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2566,14 +2566,14 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1948</v>
+        <v>1957</v>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>103.2</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2589,14 +2589,14 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1948</v>
+        <v>1958</v>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>101.6</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2612,10 +2612,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1949</v>
+        <v>1959</v>
       </c>
       <c r="B86" t="n">
-        <v>68.59999999999998</v>
+        <v>112</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2635,14 +2635,14 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1949</v>
+        <v>1960</v>
       </c>
       <c r="B87" t="n">
-        <v>73.79999999999997</v>
+        <v>111.8</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2658,14 +2658,14 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1949</v>
+        <v>1961</v>
       </c>
       <c r="B88" t="n">
-        <v>5.1</v>
+        <v>116.5</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2681,14 +2681,14 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1949</v>
+        <v>1962</v>
       </c>
       <c r="B89" t="n">
-        <v>0.1000000000000002</v>
+        <v>127.6000000000001</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2704,14 +2704,14 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1949</v>
+        <v>1963</v>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>134.9999999999999</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2727,14 +2727,14 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1949</v>
+        <v>1964</v>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>146.3000000000001</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1950</v>
+        <v>1965</v>
       </c>
       <c r="B92" t="n">
-        <v>78.90000000000002</v>
+        <v>163.5</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2773,14 +2773,14 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1950</v>
+        <v>1966</v>
       </c>
       <c r="B93" t="n">
-        <v>84.80000000000001</v>
+        <v>175.8999999999999</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2796,14 +2796,14 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1950</v>
+        <v>1967</v>
       </c>
       <c r="B94" t="n">
-        <v>5.8</v>
+        <v>177.4999999999999</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2819,14 +2819,14 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1950</v>
+        <v>1968</v>
       </c>
       <c r="B95" t="n">
-        <v>0.0999999999999998</v>
+        <v>189.3000000000001</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2842,14 +2842,14 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1950</v>
+        <v>1969</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>194.3</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2865,14 +2865,14 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1950</v>
+        <v>1970</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>187.7999999999998</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2888,10 +2888,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1951</v>
+        <v>1971</v>
       </c>
       <c r="B98" t="n">
-        <v>89.59999999999999</v>
+        <v>208.4999999999999</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2911,14 +2911,14 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1951</v>
+        <v>1972</v>
       </c>
       <c r="B99" t="n">
-        <v>96.5</v>
+        <v>237</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2934,14 +2934,14 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1951</v>
+        <v>1973</v>
       </c>
       <c r="B100" t="n">
-        <v>6.8</v>
+        <v>270.2999999999998</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2957,14 +2957,14 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1951</v>
+        <v>1974</v>
       </c>
       <c r="B101" t="n">
-        <v>0.1000000000000004</v>
+        <v>271.2000000000001</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2980,14 +2980,14 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1951</v>
+        <v>1975</v>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>306.2</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3003,14 +3003,14 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1951</v>
+        <v>1976</v>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>342.8999999999999</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3026,10 +3026,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1952</v>
+        <v>1977</v>
       </c>
       <c r="B104" t="n">
-        <v>88.10000000000005</v>
+        <v>391.8999999999999</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -3049,14 +3049,14 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1952</v>
+        <v>1978</v>
       </c>
       <c r="B105" t="n">
-        <v>96.40000000000003</v>
+        <v>447.4000000000003</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3072,14 +3072,14 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1952</v>
+        <v>1979</v>
       </c>
       <c r="B106" t="n">
-        <v>8.199999999999998</v>
+        <v>475.5999999999997</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3095,14 +3095,14 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1952</v>
+        <v>1980</v>
       </c>
       <c r="B107" t="n">
-        <v>0.1</v>
+        <v>477.1999999999996</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3118,14 +3118,14 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1952</v>
+        <v>1981</v>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>555.0000000000005</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3141,14 +3141,14 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1952</v>
+        <v>1982</v>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>555.8999999999996</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3164,10 +3164,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1953</v>
+        <v>1983</v>
       </c>
       <c r="B110" t="n">
-        <v>88.10000000000002</v>
+        <v>628.3000000000001</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -3187,14 +3187,14 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1953</v>
+        <v>1984</v>
       </c>
       <c r="B111" t="n">
-        <v>97.50000000000004</v>
+        <v>767.9000000000002</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3210,14 +3210,14 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1953</v>
+        <v>1985</v>
       </c>
       <c r="B112" t="n">
-        <v>9.4</v>
+        <v>811.7999999999997</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3233,14 +3233,14 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1953</v>
+        <v>1986</v>
       </c>
       <c r="B113" t="n">
-        <v>0</v>
+        <v>824.1000000000005</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3256,14 +3256,14 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1953</v>
+        <v>1987</v>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>894.9999999999998</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3279,14 +3279,14 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1953</v>
+        <v>1988</v>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>995.1999999999996</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3302,10 +3302,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1954</v>
+        <v>1989</v>
       </c>
       <c r="B116" t="n">
-        <v>87.59999999999998</v>
+        <v>1048.7</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -3325,14 +3325,14 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1954</v>
+        <v>1990</v>
       </c>
       <c r="B117" t="n">
-        <v>98.49999999999996</v>
+        <v>1061.1</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3348,14 +3348,14 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1954</v>
+        <v>1991</v>
       </c>
       <c r="B118" t="n">
-        <v>10.8</v>
+        <v>1061.600000000001</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3371,14 +3371,14 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1954</v>
+        <v>1992</v>
       </c>
       <c r="B119" t="n">
-        <v>0.1000000000000005</v>
+        <v>1125.3</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3394,14 +3394,14 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1954</v>
+        <v>1993</v>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>1191.599999999999</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3417,14 +3417,14 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1954</v>
+        <v>1994</v>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>1322.4</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3440,10 +3440,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1955</v>
+        <v>1995</v>
       </c>
       <c r="B122" t="n">
-        <v>100.2</v>
+        <v>1421.8</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -3463,14 +3463,14 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1955</v>
+        <v>1996</v>
       </c>
       <c r="B123" t="n">
-        <v>112</v>
+        <v>1587.4</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3486,14 +3486,14 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1955</v>
+        <v>1997</v>
       </c>
       <c r="B124" t="n">
-        <v>11.7</v>
+        <v>1739.499999999999</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3509,14 +3509,14 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1955</v>
+        <v>1998</v>
       </c>
       <c r="B125" t="n">
-        <v>0.1000000000000002</v>
+        <v>1808.299999999999</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3532,14 +3532,14 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1955</v>
+        <v>1999</v>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>1886.900000000001</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3555,14 +3555,14 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1955</v>
+        <v>2000</v>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>1961.4</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3578,10 +3578,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1956</v>
+        <v>2001</v>
       </c>
       <c r="B128" t="n">
-        <v>101.1</v>
+        <v>1968.300000000001</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -3601,14 +3601,14 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1956</v>
+        <v>2002</v>
       </c>
       <c r="B129" t="n">
-        <v>113.7</v>
+        <v>1996.1</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3624,14 +3624,14 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1956</v>
+        <v>2003</v>
       </c>
       <c r="B130" t="n">
-        <v>12.5</v>
+        <v>2102.3</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3647,14 +3647,14 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1956</v>
+        <v>2004</v>
       </c>
       <c r="B131" t="n">
-        <v>0.0999999999999998</v>
+        <v>2390.699999999998</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3670,14 +3670,14 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1956</v>
+        <v>2005</v>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>2670.6</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3693,14 +3693,14 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1956</v>
+        <v>2006</v>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>2943.7</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3716,10 +3716,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1957</v>
+        <v>2007</v>
       </c>
       <c r="B134" t="n">
-        <v>103.2</v>
+        <v>2817.5</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -3739,14 +3739,14 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1957</v>
+        <v>2008</v>
       </c>
       <c r="B135" t="n">
-        <v>116.9</v>
+        <v>2693.599999999999</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3762,14 +3762,14 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1957</v>
+        <v>2009</v>
       </c>
       <c r="B136" t="n">
-        <v>13.6</v>
+        <v>2533.800000000002</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3785,14 +3785,14 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1957</v>
+        <v>2010</v>
       </c>
       <c r="B137" t="n">
-        <v>0.1000000000000003</v>
+        <v>2957.5</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3808,14 +3808,14 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1957</v>
+        <v>2011</v>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>3095.9</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3831,14 +3831,14 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1957</v>
+        <v>1947</v>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>67.29999999999998</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3854,14 +3854,14 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1958</v>
+        <v>1948</v>
       </c>
       <c r="B140" t="n">
-        <v>101.6</v>
+        <v>79.80000000000001</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3877,10 +3877,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1958</v>
+        <v>1949</v>
       </c>
       <c r="B141" t="n">
-        <v>116.5</v>
+        <v>73.79999999999997</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -3900,14 +3900,14 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1958</v>
+        <v>1950</v>
       </c>
       <c r="B142" t="n">
-        <v>14.9</v>
+        <v>84.80000000000001</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3923,14 +3923,14 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1958</v>
+        <v>1951</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>96.49999999999999</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3946,14 +3946,14 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1958</v>
+        <v>1952</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>96.40000000000005</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3969,14 +3969,14 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1958</v>
+        <v>1953</v>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>97.50000000000003</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3992,14 +3992,14 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1959</v>
+        <v>1954</v>
       </c>
       <c r="B146" t="n">
-        <v>112</v>
+        <v>98.49999999999997</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4015,10 +4015,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1959</v>
+        <v>1955</v>
       </c>
       <c r="B147" t="n">
-        <v>129.6</v>
+        <v>112</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -4038,14 +4038,14 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1959</v>
+        <v>1956</v>
       </c>
       <c r="B148" t="n">
-        <v>16.5</v>
+        <v>113.7</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4061,14 +4061,14 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="B149" t="n">
-        <v>0.0999999999999996</v>
+        <v>116.9</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4084,14 +4084,14 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B150" t="n">
-        <v>0</v>
+        <v>116.5</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4110,11 +4110,11 @@
         <v>1959</v>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>129.6</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4133,11 +4133,11 @@
         <v>1960</v>
       </c>
       <c r="B152" t="n">
-        <v>111.8</v>
+        <v>130.8</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4153,10 +4153,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="B153" t="n">
-        <v>130.8</v>
+        <v>136.8</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -4176,14 +4176,14 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="B154" t="n">
-        <v>18</v>
+        <v>149.5000000000001</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4199,14 +4199,14 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="B155" t="n">
-        <v>0.0999999999999992</v>
+        <v>158.7999999999999</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4222,14 +4222,14 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1960</v>
+        <v>1964</v>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>171.1000000000001</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4245,14 +4245,14 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1960</v>
+        <v>1965</v>
       </c>
       <c r="B157" t="n">
-        <v>0.9</v>
+        <v>189.7</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4268,14 +4268,14 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1961</v>
+        <v>1966</v>
       </c>
       <c r="B158" t="n">
-        <v>116.5</v>
+        <v>203.1</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4291,10 +4291,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1961</v>
+        <v>1967</v>
       </c>
       <c r="B159" t="n">
-        <v>136.8</v>
+        <v>205.7999999999999</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -4314,14 +4314,14 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1961</v>
+        <v>1968</v>
       </c>
       <c r="B160" t="n">
-        <v>19.4</v>
+        <v>218.6000000000001</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4337,14 +4337,14 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1961</v>
+        <v>1969</v>
       </c>
       <c r="B161" t="n">
-        <v>0.1000000000000007</v>
+        <v>225.3</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4360,14 +4360,14 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1961</v>
+        <v>1970</v>
       </c>
       <c r="B162" t="n">
-        <v>0</v>
+        <v>219.2999999999998</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4383,14 +4383,14 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1961</v>
+        <v>1971</v>
       </c>
       <c r="B163" t="n">
-        <v>0.8</v>
+        <v>243.3</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4406,14 +4406,14 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1962</v>
+        <v>1972</v>
       </c>
       <c r="B164" t="n">
-        <v>127.6000000000001</v>
+        <v>275.4</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4429,10 +4429,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>1962</v>
+        <v>1973</v>
       </c>
       <c r="B165" t="n">
-        <v>149.5000000000001</v>
+        <v>310.2999999999999</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -4452,14 +4452,14 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1962</v>
+        <v>1974</v>
       </c>
       <c r="B166" t="n">
-        <v>21</v>
+        <v>314.1000000000001</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4475,14 +4475,14 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>1962</v>
+        <v>1975</v>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>351.0000000000001</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4498,14 +4498,14 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1962</v>
+        <v>1976</v>
       </c>
       <c r="B168" t="n">
-        <v>0</v>
+        <v>392.1999999999999</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4521,14 +4521,14 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1962</v>
+        <v>1977</v>
       </c>
       <c r="B169" t="n">
-        <v>0.9</v>
+        <v>443.8999999999999</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4544,14 +4544,14 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1963</v>
+        <v>1978</v>
       </c>
       <c r="B170" t="n">
-        <v>134.9999999999999</v>
+        <v>508.7000000000004</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4567,10 +4567,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1963</v>
+        <v>1979</v>
       </c>
       <c r="B171" t="n">
-        <v>158.7999999999999</v>
+        <v>546.2999999999997</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -4590,14 +4590,14 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1963</v>
+        <v>1980</v>
       </c>
       <c r="B172" t="n">
-        <v>22.3</v>
+        <v>560.4999999999997</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4613,14 +4613,14 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1963</v>
+        <v>1981</v>
       </c>
       <c r="B173" t="n">
-        <v>0.0999999999999996</v>
+        <v>653.0000000000005</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4636,14 +4636,14 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1963</v>
+        <v>1982</v>
       </c>
       <c r="B174" t="n">
-        <v>0</v>
+        <v>669.1999999999996</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4659,14 +4659,14 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1963</v>
+        <v>1983</v>
       </c>
       <c r="B175" t="n">
-        <v>1.4</v>
+        <v>756.1</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4682,14 +4682,14 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1964</v>
+        <v>1984</v>
       </c>
       <c r="B176" t="n">
-        <v>146.3000000000001</v>
+        <v>910.7000000000003</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4705,10 +4705,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1964</v>
+        <v>1985</v>
       </c>
       <c r="B177" t="n">
-        <v>171.1000000000001</v>
+        <v>971.0999999999998</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -4728,14 +4728,14 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1964</v>
+        <v>1986</v>
       </c>
       <c r="B178" t="n">
-        <v>23.3</v>
+        <v>996.0000000000005</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4751,14 +4751,14 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1964</v>
+        <v>1987</v>
       </c>
       <c r="B179" t="n">
-        <v>0.2000000000000008</v>
+        <v>1078.2</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4774,14 +4774,14 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1964</v>
+        <v>1988</v>
       </c>
       <c r="B180" t="n">
-        <v>0</v>
+        <v>1198.9</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4797,14 +4797,14 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1964</v>
+        <v>1989</v>
       </c>
       <c r="B181" t="n">
-        <v>1.3</v>
+        <v>1270.4</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4820,14 +4820,14 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1965</v>
+        <v>1990</v>
       </c>
       <c r="B182" t="n">
-        <v>163.5</v>
+        <v>1298.5</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4843,10 +4843,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1965</v>
+        <v>1991</v>
       </c>
       <c r="B183" t="n">
-        <v>189.7</v>
+        <v>1317.300000000001</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -4866,14 +4866,14 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1965</v>
+        <v>1992</v>
       </c>
       <c r="B184" t="n">
-        <v>24.6</v>
+        <v>1400.2</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4889,14 +4889,14 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1965</v>
+        <v>1993</v>
       </c>
       <c r="B185" t="n">
-        <v>0.2999999999999996</v>
+        <v>1486.799999999999</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4912,14 +4912,14 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>1965</v>
+        <v>1994</v>
       </c>
       <c r="B186" t="n">
-        <v>0</v>
+        <v>1642</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4935,14 +4935,14 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1965</v>
+        <v>1995</v>
       </c>
       <c r="B187" t="n">
-        <v>1.3</v>
+        <v>1770.3</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4958,14 +4958,14 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1966</v>
+        <v>1996</v>
       </c>
       <c r="B188" t="n">
-        <v>175.8999999999999</v>
+        <v>1959</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4981,10 +4981,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>1966</v>
+        <v>1997</v>
       </c>
       <c r="B189" t="n">
-        <v>203.1</v>
+        <v>2134.799999999999</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -5004,14 +5004,14 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>1966</v>
+        <v>1998</v>
       </c>
       <c r="B190" t="n">
-        <v>25.9</v>
+        <v>2227.399999999999</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5027,14 +5027,14 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1966</v>
+        <v>1999</v>
       </c>
       <c r="B191" t="n">
-        <v>0.3000000000000007</v>
+        <v>2342.6</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5050,14 +5050,14 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>1966</v>
+        <v>2000</v>
       </c>
       <c r="B192" t="n">
-        <v>0</v>
+        <v>2444.9</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5073,14 +5073,14 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>1966</v>
+        <v>2001</v>
       </c>
       <c r="B193" t="n">
-        <v>1</v>
+        <v>2479.900000000001</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5096,14 +5096,14 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>1967</v>
+        <v>2002</v>
       </c>
       <c r="B194" t="n">
-        <v>177.4999999999999</v>
+        <v>2521.6</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5119,10 +5119,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>1967</v>
+        <v>2003</v>
       </c>
       <c r="B195" t="n">
-        <v>205.8</v>
+        <v>2625.4</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -5142,14 +5142,14 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>1967</v>
+        <v>2004</v>
       </c>
       <c r="B196" t="n">
-        <v>27</v>
+        <v>2926.199999999998</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5165,14 +5165,14 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>1967</v>
+        <v>2005</v>
       </c>
       <c r="B197" t="n">
-        <v>0.399999999999999</v>
+        <v>3235.9</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -5188,14 +5188,14 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>1967</v>
+        <v>2006</v>
       </c>
       <c r="B198" t="n">
-        <v>0</v>
+        <v>3539.8</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5211,14 +5211,14 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>1967</v>
+        <v>2007</v>
       </c>
       <c r="B199" t="n">
-        <v>0.9</v>
+        <v>3437.6</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5234,14 +5234,14 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>1968</v>
+        <v>2008</v>
       </c>
       <c r="B200" t="n">
-        <v>189.3000000000001</v>
+        <v>3375</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5257,10 +5257,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>1968</v>
+        <v>2009</v>
       </c>
       <c r="B201" t="n">
-        <v>218.6000000000001</v>
+        <v>3218.400000000001</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -5280,14 +5280,14 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1968</v>
+        <v>2010</v>
       </c>
       <c r="B202" t="n">
-        <v>27.6</v>
+        <v>3627</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5303,14 +5303,14 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>1968</v>
+        <v>2011</v>
       </c>
       <c r="B203" t="n">
-        <v>0.5</v>
+        <v>3767.5</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-B</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5326,14 +5326,14 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>1968</v>
+        <v>1947</v>
       </c>
       <c r="B204" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5349,14 +5349,14 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>1968</v>
+        <v>1948</v>
       </c>
       <c r="B205" t="n">
-        <v>1.2</v>
+        <v>4.600000000000001</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5372,14 +5372,14 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>1969</v>
+        <v>1949</v>
       </c>
       <c r="B206" t="n">
-        <v>194.3</v>
+        <v>5.1</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5395,14 +5395,14 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1969</v>
+        <v>1950</v>
       </c>
       <c r="B207" t="n">
-        <v>225.3</v>
+        <v>5.8</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -5418,10 +5418,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1969</v>
+        <v>1951</v>
       </c>
       <c r="B208" t="n">
-        <v>29.40000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -5441,14 +5441,14 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1969</v>
+        <v>1952</v>
       </c>
       <c r="B209" t="n">
-        <v>0.5999999999999996</v>
+        <v>8.199999999999998</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -5464,14 +5464,14 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1969</v>
+        <v>1953</v>
       </c>
       <c r="B210" t="n">
-        <v>0</v>
+        <v>9.399999999999999</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -5487,14 +5487,14 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1969</v>
+        <v>1954</v>
       </c>
       <c r="B211" t="n">
-        <v>1</v>
+        <v>10.8</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -5510,14 +5510,14 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>1970</v>
+        <v>1955</v>
       </c>
       <c r="B212" t="n">
-        <v>187.7999999999998</v>
+        <v>11.7</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -5533,14 +5533,14 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1970</v>
+        <v>1956</v>
       </c>
       <c r="B213" t="n">
-        <v>219.2999999999998</v>
+        <v>12.5</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -5556,10 +5556,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1970</v>
+        <v>1957</v>
       </c>
       <c r="B214" t="n">
-        <v>30.8</v>
+        <v>13.6</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -5579,14 +5579,14 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1970</v>
+        <v>1958</v>
       </c>
       <c r="B215" t="n">
-        <v>0.7000000000000002</v>
+        <v>14.9</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -5602,14 +5602,14 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>1970</v>
+        <v>1959</v>
       </c>
       <c r="B216" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -5625,14 +5625,14 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>1970</v>
+        <v>1960</v>
       </c>
       <c r="B217" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5648,14 +5648,14 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1971</v>
+        <v>1961</v>
       </c>
       <c r="B218" t="n">
-        <v>208.5</v>
+        <v>19.4</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -5671,14 +5671,14 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>1971</v>
+        <v>1962</v>
       </c>
       <c r="B219" t="n">
-        <v>243.3</v>
+        <v>21</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5694,10 +5694,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1971</v>
+        <v>1963</v>
       </c>
       <c r="B220" t="n">
-        <v>34.1</v>
+        <v>22.3</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -5717,14 +5717,14 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1971</v>
+        <v>1964</v>
       </c>
       <c r="B221" t="n">
-        <v>0.9000000000000012</v>
+        <v>23.3</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5740,14 +5740,14 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1971</v>
+        <v>1965</v>
       </c>
       <c r="B222" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -5763,14 +5763,14 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1971</v>
+        <v>1966</v>
       </c>
       <c r="B223" t="n">
-        <v>-0.2</v>
+        <v>25.9</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -5786,14 +5786,14 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1972</v>
+        <v>1967</v>
       </c>
       <c r="B224" t="n">
-        <v>237</v>
+        <v>27</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -5809,14 +5809,14 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1972</v>
+        <v>1968</v>
       </c>
       <c r="B225" t="n">
-        <v>275.4</v>
+        <v>27.6</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -5832,10 +5832,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="B226" t="n">
-        <v>36.8</v>
+        <v>29.40000000000001</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -5855,14 +5855,14 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="B227" t="n">
-        <v>1.100000000000004</v>
+        <v>30.8</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -5878,14 +5878,14 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B228" t="n">
-        <v>0</v>
+        <v>34.1</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -5904,11 +5904,11 @@
         <v>1972</v>
       </c>
       <c r="B229" t="n">
-        <v>0.5</v>
+        <v>36.8</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -5927,11 +5927,11 @@
         <v>1973</v>
       </c>
       <c r="B230" t="n">
-        <v>270.2999999999998</v>
+        <v>39.3</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -5947,14 +5947,14 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="B231" t="n">
-        <v>310.2999999999999</v>
+        <v>42.59999999999999</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5970,10 +5970,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="B232" t="n">
-        <v>39.3</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -5993,14 +5993,14 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1973</v>
+        <v>1976</v>
       </c>
       <c r="B233" t="n">
-        <v>1.099999999999999</v>
+        <v>49.50000000000001</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6016,14 +6016,14 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1973</v>
+        <v>1977</v>
       </c>
       <c r="B234" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -6039,14 +6039,14 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1973</v>
+        <v>1978</v>
       </c>
       <c r="B235" t="n">
-        <v>-0.4</v>
+        <v>61.40000000000002</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -6062,14 +6062,14 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>1974</v>
+        <v>1979</v>
       </c>
       <c r="B236" t="n">
-        <v>271.2000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6085,14 +6085,14 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>1974</v>
+        <v>1980</v>
       </c>
       <c r="B237" t="n">
-        <v>314.1000000000001</v>
+        <v>85</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -6108,10 +6108,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1974</v>
+        <v>1981</v>
       </c>
       <c r="B238" t="n">
-        <v>42.6</v>
+        <v>99.20000000000003</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -6131,14 +6131,14 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1974</v>
+        <v>1982</v>
       </c>
       <c r="B239" t="n">
-        <v>1.199999999999999</v>
+        <v>112.3</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -6154,14 +6154,14 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1974</v>
+        <v>1983</v>
       </c>
       <c r="B240" t="n">
-        <v>0</v>
+        <v>124.1</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6177,14 +6177,14 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1974</v>
+        <v>1984</v>
       </c>
       <c r="B241" t="n">
-        <v>-0.9</v>
+        <v>136</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -6200,14 +6200,14 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1975</v>
+        <v>1985</v>
       </c>
       <c r="B242" t="n">
-        <v>306.2</v>
+        <v>150.1</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6223,14 +6223,14 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1975</v>
+        <v>1986</v>
       </c>
       <c r="B243" t="n">
-        <v>351.0000000000001</v>
+        <v>161.3</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6246,10 +6246,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>1975</v>
+        <v>1987</v>
       </c>
       <c r="B244" t="n">
-        <v>46.40000000000001</v>
+        <v>173.2</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -6269,14 +6269,14 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>1975</v>
+        <v>1988</v>
       </c>
       <c r="B245" t="n">
-        <v>1.600000000000003</v>
+        <v>190.2</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -6292,14 +6292,14 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>1975</v>
+        <v>1989</v>
       </c>
       <c r="B246" t="n">
-        <v>0</v>
+        <v>205.2</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -6315,14 +6315,14 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1975</v>
+        <v>1990</v>
       </c>
       <c r="B247" t="n">
-        <v>-3.2</v>
+        <v>223.8</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -6338,14 +6338,14 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>1976</v>
+        <v>1991</v>
       </c>
       <c r="B248" t="n">
-        <v>342.8999999999999</v>
+        <v>237.2</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -6361,14 +6361,14 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1976</v>
+        <v>1992</v>
       </c>
       <c r="B249" t="n">
-        <v>392.1999999999999</v>
+        <v>253.1</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -6384,10 +6384,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1976</v>
+        <v>1993</v>
       </c>
       <c r="B250" t="n">
-        <v>49.50000000000001</v>
+        <v>270.9999999999999</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -6407,14 +6407,14 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>1976</v>
+        <v>1994</v>
       </c>
       <c r="B251" t="n">
-        <v>1.6</v>
+        <v>295.3</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -6430,14 +6430,14 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>1976</v>
+        <v>1995</v>
       </c>
       <c r="B252" t="n">
-        <v>0</v>
+        <v>319.4</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -6453,14 +6453,14 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>1976</v>
+        <v>1996</v>
       </c>
       <c r="B253" t="n">
-        <v>-1.8</v>
+        <v>339.9</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -6476,14 +6476,14 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>1977</v>
+        <v>1997</v>
       </c>
       <c r="B254" t="n">
-        <v>391.8999999999999</v>
+        <v>362.9</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -6499,14 +6499,14 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>1977</v>
+        <v>1998</v>
       </c>
       <c r="B255" t="n">
-        <v>443.8999999999999</v>
+        <v>386.6</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -6522,10 +6522,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>1977</v>
+        <v>1999</v>
       </c>
       <c r="B256" t="n">
-        <v>53</v>
+        <v>422.1</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -6545,14 +6545,14 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>1977</v>
+        <v>2000</v>
       </c>
       <c r="B257" t="n">
-        <v>1.700000000000004</v>
+        <v>455</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -6568,14 +6568,14 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>1977</v>
+        <v>2001</v>
       </c>
       <c r="B258" t="n">
-        <v>0</v>
+        <v>487.8</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -6591,14 +6591,14 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>1977</v>
+        <v>2002</v>
       </c>
       <c r="B259" t="n">
-        <v>-2.7</v>
+        <v>499.8000000000001</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6614,14 +6614,14 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1978</v>
+        <v>2003</v>
       </c>
       <c r="B260" t="n">
-        <v>447.4000000000003</v>
+        <v>498.1</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -6637,14 +6637,14 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1978</v>
+        <v>2004</v>
       </c>
       <c r="B261" t="n">
-        <v>508.7000000000004</v>
+        <v>517.2</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -6660,10 +6660,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1978</v>
+        <v>2005</v>
       </c>
       <c r="B262" t="n">
-        <v>61.40000000000002</v>
+        <v>552.9</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -6683,14 +6683,14 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1978</v>
+        <v>2006</v>
       </c>
       <c r="B263" t="n">
-        <v>2.100000000000009</v>
+        <v>585.2</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -6706,14 +6706,14 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1978</v>
+        <v>2007</v>
       </c>
       <c r="B264" t="n">
-        <v>0</v>
+        <v>615.9</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -6729,14 +6729,14 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1978</v>
+        <v>2008</v>
       </c>
       <c r="B265" t="n">
-        <v>-2.2</v>
+        <v>680.3999999999999</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -6752,14 +6752,14 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1979</v>
+        <v>2009</v>
       </c>
       <c r="B266" t="n">
-        <v>475.5999999999997</v>
+        <v>684.0000000000002</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -6775,14 +6775,14 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1979</v>
+        <v>2010</v>
       </c>
       <c r="B267" t="n">
-        <v>546.2999999999997</v>
+        <v>674.0999999999999</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-C</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -6798,10 +6798,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1979</v>
+        <v>2011</v>
       </c>
       <c r="B268" t="n">
-        <v>71.09999999999999</v>
+        <v>682.9000000000001</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1979</v>
+        <v>1947</v>
       </c>
       <c r="B269" t="n">
-        <v>2.500000000000007</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -6844,14 +6844,14 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1979</v>
+        <v>1948</v>
       </c>
       <c r="B270" t="n">
-        <v>0</v>
+        <v>0.1000000000000002</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -6867,14 +6867,14 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1979</v>
+        <v>1949</v>
       </c>
       <c r="B271" t="n">
-        <v>-2.9</v>
+        <v>0.1000000000000002</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -6890,14 +6890,14 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1980</v>
+        <v>1950</v>
       </c>
       <c r="B272" t="n">
-        <v>477.1999999999997</v>
+        <v>0.09999999999999987</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -6913,14 +6913,14 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1980</v>
+        <v>1951</v>
       </c>
       <c r="B273" t="n">
-        <v>560.4999999999997</v>
+        <v>0.1000000000000004</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -6936,14 +6936,14 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1980</v>
+        <v>1952</v>
       </c>
       <c r="B274" t="n">
-        <v>85</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -6959,10 +6959,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1980</v>
+        <v>1953</v>
       </c>
       <c r="B275" t="n">
-        <v>3.400000000000011</v>
+        <v>0</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -6982,14 +6982,14 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1980</v>
+        <v>1954</v>
       </c>
       <c r="B276" t="n">
-        <v>0</v>
+        <v>0.1000000000000005</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7005,14 +7005,14 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>1980</v>
+        <v>1955</v>
       </c>
       <c r="B277" t="n">
-        <v>-5.1</v>
+        <v>0.1000000000000002</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7028,14 +7028,14 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1981</v>
+        <v>1956</v>
       </c>
       <c r="B278" t="n">
-        <v>555.0000000000005</v>
+        <v>0.09999999999999987</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -7051,14 +7051,14 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1981</v>
+        <v>1957</v>
       </c>
       <c r="B279" t="n">
-        <v>653.0000000000005</v>
+        <v>0.1000000000000003</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7074,14 +7074,14 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1981</v>
+        <v>1958</v>
       </c>
       <c r="B280" t="n">
-        <v>99.20000000000005</v>
+        <v>0</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7097,10 +7097,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>1981</v>
+        <v>1959</v>
       </c>
       <c r="B281" t="n">
-        <v>4.400000000000002</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -7120,14 +7120,14 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1981</v>
+        <v>1960</v>
       </c>
       <c r="B282" t="n">
-        <v>0</v>
+        <v>0.0999999999999992</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -7143,14 +7143,14 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>1981</v>
+        <v>1961</v>
       </c>
       <c r="B283" t="n">
-        <v>-5.6</v>
+        <v>0.1000000000000008</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -7166,14 +7166,14 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1982</v>
+        <v>1962</v>
       </c>
       <c r="B284" t="n">
-        <v>555.8999999999996</v>
+        <v>0</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -7189,14 +7189,14 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1982</v>
+        <v>1963</v>
       </c>
       <c r="B285" t="n">
-        <v>669.1999999999996</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -7212,14 +7212,14 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1982</v>
+        <v>1964</v>
       </c>
       <c r="B286" t="n">
-        <v>112.3</v>
+        <v>0.2000000000000008</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -7235,10 +7235,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1982</v>
+        <v>1965</v>
       </c>
       <c r="B287" t="n">
-        <v>5.499999999999995</v>
+        <v>0.2999999999999996</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -7258,14 +7258,14 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>1982</v>
+        <v>1966</v>
       </c>
       <c r="B288" t="n">
-        <v>0</v>
+        <v>0.3000000000000007</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -7281,14 +7281,14 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>1982</v>
+        <v>1967</v>
       </c>
       <c r="B289" t="n">
-        <v>-4.5</v>
+        <v>0.399999999999999</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -7304,14 +7304,14 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1983</v>
+        <v>1968</v>
       </c>
       <c r="B290" t="n">
-        <v>628.3000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -7327,14 +7327,14 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>1983</v>
+        <v>1969</v>
       </c>
       <c r="B291" t="n">
-        <v>756.1</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -7350,14 +7350,14 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>1983</v>
+        <v>1970</v>
       </c>
       <c r="B292" t="n">
-        <v>124.1</v>
+        <v>0.7000000000000002</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -7373,10 +7373,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>1983</v>
+        <v>1971</v>
       </c>
       <c r="B293" t="n">
-        <v>6.899999999999997</v>
+        <v>0.9000000000000012</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -7396,14 +7396,14 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>1983</v>
+        <v>1972</v>
       </c>
       <c r="B294" t="n">
-        <v>0</v>
+        <v>1.100000000000004</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -7419,14 +7419,14 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>1983</v>
+        <v>1973</v>
       </c>
       <c r="B295" t="n">
-        <v>-3.2</v>
+        <v>1.099999999999999</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -7442,14 +7442,14 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>1984</v>
+        <v>1974</v>
       </c>
       <c r="B296" t="n">
-        <v>767.9000000000002</v>
+        <v>1.199999999999999</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -7465,14 +7465,14 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>1984</v>
+        <v>1975</v>
       </c>
       <c r="B297" t="n">
-        <v>910.7000000000004</v>
+        <v>1.600000000000003</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -7488,14 +7488,14 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>1984</v>
+        <v>1976</v>
       </c>
       <c r="B298" t="n">
-        <v>136</v>
+        <v>1.6</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -7511,10 +7511,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>1984</v>
+        <v>1977</v>
       </c>
       <c r="B299" t="n">
-        <v>8.699999999999994</v>
+        <v>1.700000000000004</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -7534,14 +7534,14 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>1984</v>
+        <v>1978</v>
       </c>
       <c r="B300" t="n">
-        <v>0</v>
+        <v>2.100000000000009</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -7557,14 +7557,14 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>1984</v>
+        <v>1979</v>
       </c>
       <c r="B301" t="n">
-        <v>-1.9</v>
+        <v>2.500000000000007</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -7580,14 +7580,14 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>1985</v>
+        <v>1980</v>
       </c>
       <c r="B302" t="n">
-        <v>811.7999999999997</v>
+        <v>3.400000000000011</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7603,14 +7603,14 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>1985</v>
+        <v>1981</v>
       </c>
       <c r="B303" t="n">
-        <v>971.0999999999998</v>
+        <v>4.400000000000002</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -7626,14 +7626,14 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="B304" t="n">
-        <v>150.1</v>
+        <v>5.499999999999995</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -7649,10 +7649,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="B305" t="n">
-        <v>8.600000000000005</v>
+        <v>6.899999999999997</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -7672,14 +7672,14 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B306" t="n">
-        <v>0</v>
+        <v>8.699999999999994</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -7698,11 +7698,11 @@
         <v>1985</v>
       </c>
       <c r="B307" t="n">
-        <v>0.6</v>
+        <v>8.600000000000005</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -7721,11 +7721,11 @@
         <v>1986</v>
       </c>
       <c r="B308" t="n">
-        <v>824.1000000000005</v>
+        <v>9.699999999999996</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -7741,14 +7741,14 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B309" t="n">
-        <v>996.0000000000005</v>
+        <v>9.799999999999994</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7764,14 +7764,14 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="B310" t="n">
-        <v>161.3</v>
+        <v>10.89999999999999</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -7787,10 +7787,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="B311" t="n">
-        <v>9.699999999999996</v>
+        <v>11.59999999999999</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -7810,14 +7810,14 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>1986</v>
+        <v>1990</v>
       </c>
       <c r="B312" t="n">
-        <v>0</v>
+        <v>11.99999999999999</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -7833,14 +7833,14 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>1986</v>
+        <v>1991</v>
       </c>
       <c r="B313" t="n">
-        <v>0.9</v>
+        <v>12.8</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -7856,14 +7856,14 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>1987</v>
+        <v>1992</v>
       </c>
       <c r="B314" t="n">
-        <v>894.9999999999998</v>
+        <v>13.60000000000004</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7879,14 +7879,14 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>1987</v>
+        <v>1993</v>
       </c>
       <c r="B315" t="n">
-        <v>1078.2</v>
+        <v>15.50000000000001</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7902,14 +7902,14 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>1987</v>
+        <v>1994</v>
       </c>
       <c r="B316" t="n">
-        <v>173.2</v>
+        <v>14.70000000000002</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -7925,10 +7925,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>1987</v>
+        <v>1995</v>
       </c>
       <c r="B317" t="n">
-        <v>9.799999999999994</v>
+        <v>16.00000000000005</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -7948,14 +7948,14 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>1987</v>
+        <v>1996</v>
       </c>
       <c r="B318" t="n">
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -7971,14 +7971,14 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>1987</v>
+        <v>1997</v>
       </c>
       <c r="B319" t="n">
-        <v>0.2</v>
+        <v>18.30000000000001</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -7994,14 +7994,14 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>1988</v>
+        <v>1998</v>
       </c>
       <c r="B320" t="n">
-        <v>995.1999999999996</v>
+        <v>19.19999999999998</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -8017,14 +8017,14 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>1988</v>
+        <v>1999</v>
       </c>
       <c r="B321" t="n">
-        <v>1198.9</v>
+        <v>19.5</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -8040,14 +8040,14 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>1988</v>
+        <v>2000</v>
       </c>
       <c r="B322" t="n">
-        <v>190.2</v>
+        <v>19.40000000000003</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -8063,10 +8063,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>1988</v>
+        <v>2001</v>
       </c>
       <c r="B323" t="n">
-        <v>10.89999999999999</v>
+        <v>19.8</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -8086,14 +8086,14 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>1988</v>
+        <v>2002</v>
       </c>
       <c r="B324" t="n">
-        <v>0</v>
+        <v>19.39999999999999</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -8109,14 +8109,14 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>1988</v>
+        <v>2003</v>
       </c>
       <c r="B325" t="n">
-        <v>2.6</v>
+        <v>17.99999999999996</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -8132,14 +8132,14 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>1989</v>
+        <v>2004</v>
       </c>
       <c r="B326" t="n">
-        <v>1048.7</v>
+        <v>17.09999999999996</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -8155,14 +8155,14 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>1989</v>
+        <v>2005</v>
       </c>
       <c r="B327" t="n">
-        <v>1270.4</v>
+        <v>15.90000000000003</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -8178,14 +8178,14 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>1989</v>
+        <v>2006</v>
       </c>
       <c r="B328" t="n">
-        <v>205.2</v>
+        <v>15.09999999999994</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -8201,10 +8201,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>1989</v>
+        <v>2007</v>
       </c>
       <c r="B329" t="n">
-        <v>11.59999999999999</v>
+        <v>16.00000000000007</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -8224,14 +8224,14 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>1989</v>
+        <v>2008</v>
       </c>
       <c r="B330" t="n">
-        <v>0</v>
+        <v>16.99999999999999</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -8247,14 +8247,14 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>1989</v>
+        <v>2009</v>
       </c>
       <c r="B331" t="n">
-        <v>4.9</v>
+        <v>16.19999999999993</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -8270,14 +8270,14 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>1990</v>
+        <v>2010</v>
       </c>
       <c r="B332" t="n">
-        <v>1061.1</v>
+        <v>14.89999999999991</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -8293,14 +8293,14 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>1990</v>
+        <v>2011</v>
       </c>
       <c r="B333" t="n">
-        <v>1298.5</v>
+        <v>15.19999999999997</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-D</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -8316,14 +8316,14 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>1990</v>
+        <v>1947</v>
       </c>
       <c r="B334" t="n">
-        <v>223.8</v>
+        <v>0</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -8339,14 +8339,14 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>1990</v>
+        <v>1948</v>
       </c>
       <c r="B335" t="n">
-        <v>11.99999999999999</v>
+        <v>0</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -8362,7 +8362,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>1990</v>
+        <v>1949</v>
       </c>
       <c r="B336" t="n">
         <v>0</v>
@@ -8385,14 +8385,14 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>1990</v>
+        <v>1950</v>
       </c>
       <c r="B337" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -8408,14 +8408,14 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>1991</v>
+        <v>1951</v>
       </c>
       <c r="B338" t="n">
-        <v>1061.600000000001</v>
+        <v>0</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -8431,14 +8431,14 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>1991</v>
+        <v>1952</v>
       </c>
       <c r="B339" t="n">
-        <v>1317.300000000001</v>
+        <v>0</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -8454,14 +8454,14 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>1991</v>
+        <v>1953</v>
       </c>
       <c r="B340" t="n">
-        <v>237.2</v>
+        <v>0</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -8477,14 +8477,14 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>1991</v>
+        <v>1954</v>
       </c>
       <c r="B341" t="n">
-        <v>12.8</v>
+        <v>0</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -8500,7 +8500,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>1991</v>
+        <v>1955</v>
       </c>
       <c r="B342" t="n">
         <v>0</v>
@@ -8523,14 +8523,14 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>1991</v>
+        <v>1956</v>
       </c>
       <c r="B343" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -8546,14 +8546,14 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>1992</v>
+        <v>1957</v>
       </c>
       <c r="B344" t="n">
-        <v>1125.3</v>
+        <v>0</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -8569,14 +8569,14 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>1992</v>
+        <v>1958</v>
       </c>
       <c r="B345" t="n">
-        <v>1400.200000000001</v>
+        <v>0</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -8592,14 +8592,14 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>1992</v>
+        <v>1959</v>
       </c>
       <c r="B346" t="n">
-        <v>253.1</v>
+        <v>0</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -8615,14 +8615,14 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>1992</v>
+        <v>1960</v>
       </c>
       <c r="B347" t="n">
-        <v>13.60000000000004</v>
+        <v>0</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -8638,7 +8638,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>1992</v>
+        <v>1961</v>
       </c>
       <c r="B348" t="n">
         <v>0</v>
@@ -8661,14 +8661,14 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>1992</v>
+        <v>1962</v>
       </c>
       <c r="B349" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -8684,14 +8684,14 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>1993</v>
+        <v>1963</v>
       </c>
       <c r="B350" t="n">
-        <v>1191.599999999999</v>
+        <v>0</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -8707,14 +8707,14 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>1993</v>
+        <v>1964</v>
       </c>
       <c r="B351" t="n">
-        <v>1486.799999999999</v>
+        <v>0</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -8730,14 +8730,14 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>1993</v>
+        <v>1965</v>
       </c>
       <c r="B352" t="n">
-        <v>270.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -8753,14 +8753,14 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>1993</v>
+        <v>1966</v>
       </c>
       <c r="B353" t="n">
-        <v>15.50000000000001</v>
+        <v>0</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -8776,7 +8776,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>1993</v>
+        <v>1967</v>
       </c>
       <c r="B354" t="n">
         <v>0</v>
@@ -8799,14 +8799,14 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>1993</v>
+        <v>1968</v>
       </c>
       <c r="B355" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -8822,14 +8822,14 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>1994</v>
+        <v>1969</v>
       </c>
       <c r="B356" t="n">
-        <v>1322.4</v>
+        <v>0</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -8845,14 +8845,14 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>1994</v>
+        <v>1970</v>
       </c>
       <c r="B357" t="n">
-        <v>1642</v>
+        <v>0</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -8868,14 +8868,14 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>1994</v>
+        <v>1971</v>
       </c>
       <c r="B358" t="n">
-        <v>295.3</v>
+        <v>0</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -8891,14 +8891,14 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>1994</v>
+        <v>1972</v>
       </c>
       <c r="B359" t="n">
-        <v>14.70000000000002</v>
+        <v>0</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -8914,7 +8914,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>1994</v>
+        <v>1973</v>
       </c>
       <c r="B360" t="n">
         <v>0</v>
@@ -8937,14 +8937,14 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>1994</v>
+        <v>1974</v>
       </c>
       <c r="B361" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -8960,14 +8960,14 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>1995</v>
+        <v>1975</v>
       </c>
       <c r="B362" t="n">
-        <v>1421.799999999999</v>
+        <v>0</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -8983,14 +8983,14 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>1995</v>
+        <v>1976</v>
       </c>
       <c r="B363" t="n">
-        <v>1770.299999999999</v>
+        <v>0</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -9006,14 +9006,14 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>1995</v>
+        <v>1977</v>
       </c>
       <c r="B364" t="n">
-        <v>319.4</v>
+        <v>0</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -9029,14 +9029,14 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>1995</v>
+        <v>1978</v>
       </c>
       <c r="B365" t="n">
-        <v>16.00000000000005</v>
+        <v>0</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -9052,7 +9052,7 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>1995</v>
+        <v>1979</v>
       </c>
       <c r="B366" t="n">
         <v>0</v>
@@ -9075,14 +9075,14 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>1995</v>
+        <v>1980</v>
       </c>
       <c r="B367" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -9098,14 +9098,14 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>1996</v>
+        <v>1981</v>
       </c>
       <c r="B368" t="n">
-        <v>1587.4</v>
+        <v>0</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -9121,14 +9121,14 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>1996</v>
+        <v>1982</v>
       </c>
       <c r="B369" t="n">
-        <v>1959</v>
+        <v>0</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -9144,14 +9144,14 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>1996</v>
+        <v>1983</v>
       </c>
       <c r="B370" t="n">
-        <v>339.9</v>
+        <v>0</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -9167,14 +9167,14 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>1996</v>
+        <v>1984</v>
       </c>
       <c r="B371" t="n">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -9190,7 +9190,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>1996</v>
+        <v>1985</v>
       </c>
       <c r="B372" t="n">
         <v>0</v>
@@ -9213,14 +9213,14 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>1996</v>
+        <v>1986</v>
       </c>
       <c r="B373" t="n">
-        <v>14.4</v>
+        <v>0</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -9236,14 +9236,14 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>1997</v>
+        <v>1987</v>
       </c>
       <c r="B374" t="n">
-        <v>1739.499999999999</v>
+        <v>0</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -9259,14 +9259,14 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>1997</v>
+        <v>1988</v>
       </c>
       <c r="B375" t="n">
-        <v>2134.8</v>
+        <v>0</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -9282,14 +9282,14 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>1997</v>
+        <v>1989</v>
       </c>
       <c r="B376" t="n">
-        <v>362.9</v>
+        <v>0</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -9305,14 +9305,14 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>1997</v>
+        <v>1990</v>
       </c>
       <c r="B377" t="n">
-        <v>18.30000000000001</v>
+        <v>0</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -9328,7 +9328,7 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>1997</v>
+        <v>1991</v>
       </c>
       <c r="B378" t="n">
         <v>0</v>
@@ -9351,14 +9351,14 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>1997</v>
+        <v>1992</v>
       </c>
       <c r="B379" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -9374,14 +9374,14 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>1998</v>
+        <v>1993</v>
       </c>
       <c r="B380" t="n">
-        <v>1808.299999999999</v>
+        <v>0</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -9397,14 +9397,14 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>1998</v>
+        <v>1994</v>
       </c>
       <c r="B381" t="n">
-        <v>2227.399999999999</v>
+        <v>0</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -9420,14 +9420,14 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>1998</v>
+        <v>1995</v>
       </c>
       <c r="B382" t="n">
-        <v>386.6</v>
+        <v>0</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -9443,14 +9443,14 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="B383" t="n">
-        <v>19.19999999999998</v>
+        <v>0</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -9466,7 +9466,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B384" t="n">
         <v>0</v>
@@ -9492,11 +9492,11 @@
         <v>1998</v>
       </c>
       <c r="B385" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -9515,11 +9515,11 @@
         <v>1999</v>
       </c>
       <c r="B386" t="n">
-        <v>1886.9</v>
+        <v>0</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -9535,14 +9535,14 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B387" t="n">
-        <v>2342.6</v>
+        <v>0</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -9558,14 +9558,14 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="B388" t="n">
-        <v>422.1</v>
+        <v>0</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -9581,14 +9581,14 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="B389" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -9604,7 +9604,7 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="B390" t="n">
         <v>0</v>
@@ -9627,14 +9627,14 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>1999</v>
+        <v>2004</v>
       </c>
       <c r="B391" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -9650,14 +9650,14 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="B392" t="n">
-        <v>1961.4</v>
+        <v>0</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -9673,14 +9673,14 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>2000</v>
+        <v>2006</v>
       </c>
       <c r="B393" t="n">
-        <v>2444.9</v>
+        <v>0</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -9696,14 +9696,14 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>2000</v>
+        <v>2007</v>
       </c>
       <c r="B394" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -9719,14 +9719,14 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>2000</v>
+        <v>2008</v>
       </c>
       <c r="B395" t="n">
-        <v>19.40000000000003</v>
+        <v>0</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -9742,7 +9742,7 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>2000</v>
+        <v>2009</v>
       </c>
       <c r="B396" t="n">
         <v>0</v>
@@ -9765,14 +9765,14 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="B397" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>XS001-F</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -9788,14 +9788,14 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="B398" t="n">
-        <v>1968.300000000001</v>
+        <v>0</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-E</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -9811,14 +9811,14 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>2001</v>
+        <v>1947</v>
       </c>
       <c r="B399" t="n">
-        <v>2479.900000000001</v>
+        <v>0</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -9834,14 +9834,14 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>2001</v>
+        <v>1948</v>
       </c>
       <c r="B400" t="n">
-        <v>487.8</v>
+        <v>0</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -9857,14 +9857,14 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>2001</v>
+        <v>1949</v>
       </c>
       <c r="B401" t="n">
-        <v>19.8</v>
+        <v>0</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -9880,14 +9880,14 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>2001</v>
+        <v>1950</v>
       </c>
       <c r="B402" t="n">
         <v>0</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -9903,10 +9903,10 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>2001</v>
+        <v>1951</v>
       </c>
       <c r="B403" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
@@ -9926,14 +9926,14 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>2002</v>
+        <v>1952</v>
       </c>
       <c r="B404" t="n">
-        <v>1996.1</v>
+        <v>0</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -9949,14 +9949,14 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>2002</v>
+        <v>1953</v>
       </c>
       <c r="B405" t="n">
-        <v>2521.6</v>
+        <v>0</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -9972,14 +9972,14 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>2002</v>
+        <v>1954</v>
       </c>
       <c r="B406" t="n">
-        <v>499.8000000000001</v>
+        <v>0</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -9995,14 +9995,14 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>2002</v>
+        <v>1955</v>
       </c>
       <c r="B407" t="n">
-        <v>19.39999999999999</v>
+        <v>0</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -10018,14 +10018,14 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>2002</v>
+        <v>1956</v>
       </c>
       <c r="B408" t="n">
         <v>0</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -10041,10 +10041,10 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>2002</v>
+        <v>1957</v>
       </c>
       <c r="B409" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
@@ -10064,14 +10064,14 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>2003</v>
+        <v>1958</v>
       </c>
       <c r="B410" t="n">
-        <v>2102.3</v>
+        <v>0</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -10087,14 +10087,14 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>2003</v>
+        <v>1959</v>
       </c>
       <c r="B411" t="n">
-        <v>2625.4</v>
+        <v>1</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -10110,14 +10110,14 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>2003</v>
+        <v>1960</v>
       </c>
       <c r="B412" t="n">
-        <v>498.1</v>
+        <v>0.9</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -10133,14 +10133,14 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>2003</v>
+        <v>1961</v>
       </c>
       <c r="B413" t="n">
-        <v>17.99999999999996</v>
+        <v>0.8</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -10156,14 +10156,14 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>2003</v>
+        <v>1962</v>
       </c>
       <c r="B414" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -10179,10 +10179,10 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>2003</v>
+        <v>1963</v>
       </c>
       <c r="B415" t="n">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
@@ -10202,14 +10202,14 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>2004</v>
+        <v>1964</v>
       </c>
       <c r="B416" t="n">
-        <v>2390.699999999998</v>
+        <v>1.3</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -10225,14 +10225,14 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>2004</v>
+        <v>1965</v>
       </c>
       <c r="B417" t="n">
-        <v>2926.199999999998</v>
+        <v>1.3</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -10248,14 +10248,14 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>2004</v>
+        <v>1966</v>
       </c>
       <c r="B418" t="n">
-        <v>517.2</v>
+        <v>1</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -10271,14 +10271,14 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>2004</v>
+        <v>1967</v>
       </c>
       <c r="B419" t="n">
-        <v>17.09999999999996</v>
+        <v>0.9</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -10294,14 +10294,14 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>2004</v>
+        <v>1968</v>
       </c>
       <c r="B420" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -10317,10 +10317,10 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>2004</v>
+        <v>1969</v>
       </c>
       <c r="B421" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
@@ -10340,14 +10340,14 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>2005</v>
+        <v>1970</v>
       </c>
       <c r="B422" t="n">
-        <v>2670.6</v>
+        <v>0</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -10363,14 +10363,14 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>2005</v>
+        <v>1971</v>
       </c>
       <c r="B423" t="n">
-        <v>3235.9</v>
+        <v>-0.2</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -10386,14 +10386,14 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>2005</v>
+        <v>1972</v>
       </c>
       <c r="B424" t="n">
-        <v>552.9</v>
+        <v>0.5</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -10409,14 +10409,14 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>2005</v>
+        <v>1973</v>
       </c>
       <c r="B425" t="n">
-        <v>15.90000000000003</v>
+        <v>-0.4</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -10432,14 +10432,14 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>2005</v>
+        <v>1974</v>
       </c>
       <c r="B426" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -10455,10 +10455,10 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>2005</v>
+        <v>1975</v>
       </c>
       <c r="B427" t="n">
-        <v>-3.5</v>
+        <v>-3.2</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
@@ -10478,14 +10478,14 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>2006</v>
+        <v>1976</v>
       </c>
       <c r="B428" t="n">
-        <v>2943.7</v>
+        <v>-1.8</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -10501,14 +10501,14 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>2006</v>
+        <v>1977</v>
       </c>
       <c r="B429" t="n">
-        <v>3539.8</v>
+        <v>-2.7</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -10524,14 +10524,14 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>2006</v>
+        <v>1978</v>
       </c>
       <c r="B430" t="n">
-        <v>585.2</v>
+        <v>-2.2</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -10547,14 +10547,14 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>2006</v>
+        <v>1979</v>
       </c>
       <c r="B431" t="n">
-        <v>15.09999999999994</v>
+        <v>-2.9</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -10570,14 +10570,14 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>2006</v>
+        <v>1980</v>
       </c>
       <c r="B432" t="n">
-        <v>0</v>
+        <v>-5.1</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -10593,10 +10593,10 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>2006</v>
+        <v>1981</v>
       </c>
       <c r="B433" t="n">
-        <v>-4.2</v>
+        <v>-5.6</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
@@ -10616,14 +10616,14 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>2007</v>
+        <v>1982</v>
       </c>
       <c r="B434" t="n">
-        <v>2817.5</v>
+        <v>-4.5</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -10639,14 +10639,14 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>2007</v>
+        <v>1983</v>
       </c>
       <c r="B435" t="n">
-        <v>3437.6</v>
+        <v>-3.2</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -10662,14 +10662,14 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>2007</v>
+        <v>1984</v>
       </c>
       <c r="B436" t="n">
-        <v>615.9</v>
+        <v>-1.9</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -10685,14 +10685,14 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>2007</v>
+        <v>1985</v>
       </c>
       <c r="B437" t="n">
-        <v>16.00000000000007</v>
+        <v>0.6</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -10708,14 +10708,14 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>2007</v>
+        <v>1986</v>
       </c>
       <c r="B438" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -10731,10 +10731,10 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>2007</v>
+        <v>1987</v>
       </c>
       <c r="B439" t="n">
-        <v>-11.8</v>
+        <v>0.2</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
@@ -10754,14 +10754,14 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>2008</v>
+        <v>1988</v>
       </c>
       <c r="B440" t="n">
-        <v>2693.599999999999</v>
+        <v>2.6</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -10777,14 +10777,14 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>2008</v>
+        <v>1989</v>
       </c>
       <c r="B441" t="n">
-        <v>3375</v>
+        <v>4.9</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -10800,14 +10800,14 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>2008</v>
+        <v>1990</v>
       </c>
       <c r="B442" t="n">
-        <v>680.3999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -10823,14 +10823,14 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>2008</v>
+        <v>1991</v>
       </c>
       <c r="B443" t="n">
-        <v>16.99999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -10846,14 +10846,14 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>2008</v>
+        <v>1992</v>
       </c>
       <c r="B444" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -10869,10 +10869,10 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>2008</v>
+        <v>1993</v>
       </c>
       <c r="B445" t="n">
-        <v>-16</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
@@ -10892,14 +10892,14 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>2009</v>
+        <v>1994</v>
       </c>
       <c r="B446" t="n">
-        <v>2533.800000000001</v>
+        <v>9.6</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -10915,14 +10915,14 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>2009</v>
+        <v>1995</v>
       </c>
       <c r="B447" t="n">
-        <v>3218.400000000001</v>
+        <v>13.1</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -10938,14 +10938,14 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>2009</v>
+        <v>1996</v>
       </c>
       <c r="B448" t="n">
-        <v>684.0000000000002</v>
+        <v>14.4</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -10961,14 +10961,14 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>2009</v>
+        <v>1997</v>
       </c>
       <c r="B449" t="n">
-        <v>16.19999999999993</v>
+        <v>14.1</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -10984,14 +10984,14 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>2009</v>
+        <v>1998</v>
       </c>
       <c r="B450" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -11007,10 +11007,10 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="B451" t="n">
-        <v>-15.6</v>
+        <v>14.1</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
@@ -11030,14 +11030,14 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="B452" t="n">
-        <v>2957.5</v>
+        <v>9.1</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -11053,14 +11053,14 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="B453" t="n">
-        <v>3627.000000000001</v>
+        <v>4</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -11076,14 +11076,14 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="B454" t="n">
-        <v>674.0999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -11099,14 +11099,14 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>2010</v>
+        <v>2003</v>
       </c>
       <c r="B455" t="n">
-        <v>14.89999999999991</v>
+        <v>7</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -11122,14 +11122,14 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="B456" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -11145,10 +11145,10 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="B457" t="n">
-        <v>-19.5</v>
+        <v>-3.5</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
@@ -11168,14 +11168,14 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="B458" t="n">
-        <v>3095.9</v>
+        <v>-4.2</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>XS001-A</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -11191,14 +11191,14 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="B459" t="n">
-        <v>3767.5</v>
+        <v>-11.8</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>XS001-B</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -11214,14 +11214,14 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="B460" t="n">
-        <v>682.9000000000001</v>
+        <v>-16</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>XS001-C</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -11237,14 +11237,14 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B461" t="n">
-        <v>15.19999999999997</v>
+        <v>-15.6</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>XS001-D</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -11260,14 +11260,14 @@
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B462" t="n">
-        <v>0</v>
+        <v>-19.5</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>XS001-E</t>
+          <t>XS001-F</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -11392,7 +11392,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Business NOS = Aggregate NOS - HH - NPISH - GenGov - GovEnterp. Source: Appendix Table 6.8.I.1. Used by XS003 / S602. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
+          <t>Business net operating surplus (NOS) = Aggregate NOS − households (HH) − non-profit institutions serving households (NPISH) − general government (GenGov) − government enterprises (GovEnterp). Source: Appendix Table 6.8.I.1. Used by XS003 and S602.</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
+          <t>The canonical Shaikh-published values are transcribed from the published Chapter 6 appendix workbook (Shaikh 2016, Appendix 6.8). Upstream agencies are the Bureau of Economic Analysis (BEA) — its National Income and Product Accounts (NIPA) and Fixed Asset accounts (FA) — the IRS Statistics of Income (SOI), the U.S. Census Bureau (Historical Statistics 1975, for IRS book values), and the Federal Reserve Board G.17 industrial-production release (FRB G.17). All public domain.</t>
         </is>
       </c>
     </row>
@@ -11591,7 +11591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>`V03_XS001_validate.py` round-trip-validates against the Appendix 6.8 source workbook at 1.0% tolerance. Per the Phase 4 adequacy report (`CH6_ADEQUACY_REPORT.json`), Phase 5 blockers B2 (NIPA T7.11 FISIM remap, resolver in `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
+          <t>The validation step round-trips the constructed series against the Appendix 6.8 source workbook at a 1.0% tolerance. Two data-sourcing steps needed for this construction are resolved: the remap of financial services indirectly measured (FISIM) in NIPA Table 7.11, and the 1993 BEA depreciation rates.</t>
         </is>
       </c>
     </row>
@@ -11634,7 +11634,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published XS001 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
+          <t>Under the Chapter 6 Generalized Perpetual Inventory Method (GPIM) construction pipeline, and following the principle that extended values must be rebuilt from sources rather than spliced, **extension does NOT splice the published XS001 values**. Instead, the extension re-fetches the underlying National Income and Product Accounts (NIPA), BEA Fixed Asset, IRS, and Census components and re-runs the formula end-to-end at the current vintage.</t>
         </is>
       </c>
     </row>
@@ -11644,14 +11644,14 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
+          <t>1. Fetch the BEA NIPA tables via the BEA data API (a BEA API key is required), using the table ids documented for this series' primary source.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
+          <t>2. Fetch BEA Fixed Asset Tables 6.1, 6.4, 6.7, 6.8 from the same source.</t>
         </is>
       </c>
     </row>
@@ -11681,7 +11681,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>For XS001, the Phase 5 round-trip validation reads `XS001_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1947-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
+          <t>For XS001, the round-trip validation reads the raw series from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1947-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
         </is>
       </c>
     </row>
@@ -11691,7 +11691,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>## No-Proxy Disclosure</t>
+          <t>## Source substitutions</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>## No-Synthetic Disclosure</t>
+          <t>## Forecast vs. observed data</t>
         </is>
       </c>
     </row>
@@ -11721,7 +11721,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified against the staged 1993 BEA depreciation inputs).</t>
         </is>
       </c>
     </row>
@@ -11755,35 +11755,35 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+          <t>| Appendix workbook missing or corrupted | The appendix loader raises a file-not-found error or returns an empty table | The load step returns a FAIL status naming the missing file |</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+          <t>| Variable name not in workbook | The variable lookup returns no rows | The load step records 0 rows for that subseries; validation flags it as missing |</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+          <t>| BEA / IRS vintage drift during extension | The documented re-fetch script logs the vintage year; validation tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>| FISIM T7.11 line revision (XS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+          <t>| FISIM (financial services indirectly measured) revision to NIPA Table 7.11 line numbers (affects XS003) | The Table 7.11 line resolver falls back to the nearest pinned vintage with a logged warning | Lines are re-mapped by their published stub labels; the vintage used is logged |</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>| BEA 1993 depreciation rate not available post-2011 | XS004/XS006/XS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
+          <t>| BEA 1993 depreciation rate not available post-2011 | The capital-stock series (XS004 and related) freeze depreciation-rate inputs at the 2011-vintage projection | Documented with the staged 1993 BEA methodology inputs |</t>
         </is>
       </c>
     </row>
@@ -11793,7 +11793,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>## CD2 Divergence Pre-Disclosure</t>
+          <t>## Comparison with the earlier replication</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
+          <t>Round-trip parity with an earlier replication is expected within tolerance for the book period. The comparison against that earlier replication's per-series output is informational only, when available.</t>
         </is>
       </c>
     </row>
@@ -11813,7 +11813,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>## Anti-Degradation Compliance</t>
+          <t>## Extension integrity</t>
         </is>
       </c>
     </row>
@@ -11823,7 +11823,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Per Anu Framework: extension MUST re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end. Splicing the published series is FORBIDDEN. Loader caches BEA / FRED responses per `S00_cache` with 30-day TTL (book-period values: TTL=None).</t>
+          <t>Extension MUST re-fetch the BEA, IRS, and Federal Reserve Board (FRB) component series and re-compute the formula end-to-end; splicing the published series is forbidden. The loader caches BEA and FRED responses for 30 days (book-period values are cached permanently).</t>
         </is>
       </c>
     </row>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T22:46:45.073268+00:00</t>
+          <t>2026-07-02T06:26:29.726845+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS001_extenbook.xlsx
+++ b/extenbooks/XS001_extenbook.xlsx
@@ -12323,7 +12323,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:26:29.726845+00:00</t>
+          <t>2026-07-11T03:44:26.981628+00:00</t>
         </is>
       </c>
     </row>
@@ -12338,11 +12338,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12365,6 +12365,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_6_8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Clean six-component dollar decomposition (all billions_current_usd) of aggregate NIPA NOS into the sectors Shaikh nets out to isolate for-profit business NOS. Single-unit, renders sensibly one-trace-per-component; feeds XS003/S602. Appendix Table 6.8.I.1.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS001_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS001_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Business NOS = Aggregate NOS - HH - NPISH - GenGov - GovEnterp. Source: Appendix Table 6.8.I.1. Used by XS003 / S602.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>billions_current_usd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
